--- a/artfynd/A 28582-2025 artfynd.xlsx
+++ b/artfynd/A 28582-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017255</v>
       </c>
       <c r="B2" t="n">
-        <v>92502</v>
+        <v>92510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017258</v>
       </c>
       <c r="B4" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017256</v>
       </c>
       <c r="B5" t="n">
-        <v>97216</v>
+        <v>97218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28582-2025 artfynd.xlsx
+++ b/artfynd/A 28582-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017255</v>
       </c>
       <c r="B2" t="n">
-        <v>92510</v>
+        <v>92514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017257</v>
       </c>
       <c r="B3" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017258</v>
       </c>
       <c r="B4" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017256</v>
       </c>
       <c r="B5" t="n">
-        <v>97218</v>
+        <v>97222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28582-2025 artfynd.xlsx
+++ b/artfynd/A 28582-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>126017256</v>
       </c>
       <c r="B5" t="n">
-        <v>97222</v>
+        <v>97223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28582-2025 artfynd.xlsx
+++ b/artfynd/A 28582-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017255</v>
       </c>
       <c r="B2" t="n">
-        <v>92514</v>
+        <v>92516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017257</v>
       </c>
       <c r="B3" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017258</v>
       </c>
       <c r="B4" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017256</v>
       </c>
       <c r="B5" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28582-2025 artfynd.xlsx
+++ b/artfynd/A 28582-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017255</v>
       </c>
       <c r="B2" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017258</v>
       </c>
       <c r="B4" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017256</v>
       </c>
       <c r="B5" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28582-2025 artfynd.xlsx
+++ b/artfynd/A 28582-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017255</v>
       </c>
       <c r="B2" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017258</v>
       </c>
       <c r="B4" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017256</v>
       </c>
       <c r="B5" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28582-2025 artfynd.xlsx
+++ b/artfynd/A 28582-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017255</v>
       </c>
       <c r="B2" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017257</v>
       </c>
       <c r="B3" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017258</v>
       </c>
       <c r="B4" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017256</v>
       </c>
       <c r="B5" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28582-2025 artfynd.xlsx
+++ b/artfynd/A 28582-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>126017256</v>
       </c>
       <c r="B5" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28582-2025 artfynd.xlsx
+++ b/artfynd/A 28582-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017255</v>
       </c>
       <c r="B2" t="n">
-        <v>92524</v>
+        <v>92527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017257</v>
       </c>
       <c r="B3" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017258</v>
       </c>
       <c r="B4" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126017256</v>
       </c>
       <c r="B5" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 28582-2025 artfynd.xlsx
+++ b/artfynd/A 28582-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>126017255</v>
       </c>
       <c r="B2" t="n">
-        <v>92527</v>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126017257</v>
+        <v>126017254</v>
       </c>
       <c r="B3" t="n">
-        <v>78738</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748355</v>
+        <v>748224</v>
       </c>
       <c r="R3" t="n">
-        <v>7317722</v>
+        <v>7318042</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -890,11 +890,11 @@
         <v>126017258</v>
       </c>
       <c r="B4" t="n">
-        <v>92535</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126017256</v>
+        <v>126017257</v>
       </c>
       <c r="B5" t="n">
-        <v>97245</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748139</v>
+        <v>748355</v>
       </c>
       <c r="R5" t="n">
-        <v>7317847</v>
+        <v>7317722</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,6 +1096,112 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126017256</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bredsel, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>748139</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7317847</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28582-2025 artfynd.xlsx
+++ b/artfynd/A 28582-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017258</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017257</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017255</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017254</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017256</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>